--- a/astro-site/public/dl/coffee-cart-business-plan/coffee-cart-startup-checklist.xlsx
+++ b/astro-site/public/dl/coffee-cart-business-plan/coffee-cart-startup-checklist.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Ask for catering experience. Estimated taxes are due quarterly; move a share of every event deposit into a tax savings account so the bill never surprises you.</t>
+          <t>Ask for catering experience. Estimated taxes are due quarterly; move a share of every event retainer into a tax savings account so the bill never surprises you.</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Bring your EIN letter and formation documents. Keep a card for purchases and a separate account for event deposits, so client money never mixes with personal money.</t>
+          <t>Bring your EIN letter and formation documents. Keep a card for purchases and a separate account for event retainers, so client money never mixes with personal money.</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Apply on your state tax agency website. Hosted bookings are usually taxed as catering, and in many states that means the whole invoice: coffee, baristas, extras and travel. At festivals and farmers markets you collect tax drink by drink, and you may need to register where you sell. Check your state's rule before you quote.</t>
+          <t>Apply on your state tax agency website. Hosted bookings are usually taxed as catering, and in many states that means the whole invoice: coffee, baristas and extras, and in some states travel. At festivals and farmers markets you collect tax drink by drink, and you may need to register where you sell. Check your state's rule before you quote.</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Milk is a TCS food: keep it at 41 °F (5 °C) or below (FDA Food Code minimum) in the refrigerator and in the coolers, and date every opened container. Use potable water from an approved source in food-grade tanks, wash your hands first, and wipe and purge the steam wand and clean the pitchers between drinks. Flag the allergens: milk, soy and tree nuts, plus wheat and egg in pastries. Buy pastries only from a licensed bakery.</t>
+          <t>Milk is a TCS food: keep it at 41 °F (5 °C) or below (the FDA Food Code cold-holding limit) in the refrigerator and in the coolers, and date every opened container. Use potable water from an approved source in food-grade tanks, wash your hands first, and wipe and purge the steam wand and clean the pitchers between drinks. Flag the allergens: milk, soy and tree nuts, plus wheat and egg in pastries. Buy pastries only from a licensed bakery.</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Most health departments require one certified manager. Take an ANSI-accredited exam and keep a copy for your permit file and for every event binder.</t>
+          <t>Many health departments require one certified manager. Take an ANSI-accredited exam and keep a copy for your permit file and for every event binder.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Check with your fire marshal about the generator and any propane</t>
+          <t>Check with your fire marshal about the generator</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Without grease vapors you do not need a hood, but a generator does have rules. As an example, NFPA 96 guidance (summary) keeps a generator at least 12 ft (3.7 m) from the unit and 10 ft (3 m) from buildings, with an extinguisher on hand, and New Jersey asks for a permit each time you set up with a generator. Rules differ by city and fire district: ask your fire marshal.</t>
+          <t>Without grease vapors you do not need a hood, but a generator does have rules. As one example, a city fire department checklist (Lenexa, Kansas, based on NFPA 96) asks for a free-standing generator at least 12 ft (3.7 m) from the unit and 10 ft (3 m) from buildings, with an extinguisher on hand, and some states, such as New Jersey, may require a fire safety permit where a generator is used. Rules differ by city and fire district: confirm with your fire marshal.</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Keep milk at 41 °F (5 °C) or below (FDA Food Code minimum) with an under-counter refrigerator at each station and coolers with ice packs for the reserve. Calibrate thermometers in ice water and keep spares in the trailer. Airpots keep batch brew hot through the service window.</t>
+          <t>Keep milk at 41 °F (5 °C) or below (the FDA Food Code cold-holding limit) with an under-counter refrigerator at each station and coolers with ice packs for the reserve. Calibrate thermometers in ice water and keep spares in the trailer. Airpots keep batch brew hot through the service window.</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Write a recipe and a label for each house-made syrup, and decide which milks you carry (oat, almond, soy) and whether you serve chai. Keep an allergen list per drink: milk, soy and tree nuts, and oat is gluten-free only if certified. Plan milk in oz per drink (8 oz, or 240 ml) and in gallons per event.</t>
+          <t>Write a recipe and a label for each house-made syrup, and decide which milks you carry (oat, almond, soy) and whether you serve chai. Keep an allergen list per drink: milk, soy and tree nuts, and oat is gluten-free only if labeled gluten-free. Plan milk in oz per drink (8 oz, or 240 ml) and in gallons per event.</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Check the refrigerator thermometer at each station and write down the temperature when you load, when you set up and mid-service. Milk must stay at 41 °F (5 °C) or below (FDA Food Code minimum). Keep the logs after every event.</t>
+          <t>Check the refrigerator thermometer at each station and write down the temperature when you load, when you set up and mid-service. Milk must stay at 41 °F (5 °C) or below (the FDA Food Code cold-holding limit). Keep the logs after every event.</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Run a pre-event briefing every time. Set your standards: a double shot at 18 g (0.63 oz) in and about 36 g (1.27 oz) out, 8 oz (240 ml) milk drinks, latte art, a greeting and how to move the line. Label milk, soy and tree nuts, and wheat and egg in pastries; oat milk is gluten-free only if certified.</t>
+          <t>Run a pre-event briefing every time. Set your standards: a double shot at 18 g (0.63 oz) in and about 36 g (1.27 oz) out, 8 oz (240 ml) milk drinks, latte art, a greeting and how to move the line. Label milk, soy and tree nuts, and wheat and egg in pastries; oat milk is gluten-free only if labeled gluten-free.</t>
         </is>
       </c>
     </row>
